--- a/Evolucion_Manual.xlsx
+++ b/Evolucion_Manual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gforteza\Desktop\Germán Forteza - Marketing\Wurth\Acciones y Canales\Apps\Reacti-Salvation Days\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C6CEB4-8CF4-40F3-AFA5-1EB2228CB957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D0ED08-9626-41E8-AA84-1C1CE71D0CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1DBC4893-E753-4FAB-AE0B-6A98DB130426}"/>
+    <workbookView xWindow="-28920" yWindow="-4815" windowWidth="29040" windowHeight="15720" xr2:uid="{1DBC4893-E753-4FAB-AE0B-6A98DB130426}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -32,42 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>German Forteza</author>
-  </authors>
-  <commentList>
-    <comment ref="Q2" authorId="0" shapeId="0" xr:uid="{2B50413C-684F-4A03-8483-8442A229D6AF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>German Forteza:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Este archivo antes de subirse a la plataforma deberá ser pasado a extención CSV</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="43">
   <si>
     <t>ID</t>
   </si>
@@ -190,13 +156,19 @@
   </si>
   <si>
     <t>18 de Marzo</t>
+  </si>
+  <si>
+    <t>PAULA ULERY</t>
+  </si>
+  <si>
+    <t>ELIANA MEDINA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,26 +314,20 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,13 +521,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,32 +792,35 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1214,713 +1195,1294 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C6D037-65B5-455B-BE46-93F44B164E92}">
-  <dimension ref="A1:R20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C6D037-65B5-455B-BE46-93F44B164E92}">
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
     <col min="2" max="2" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="1"/>
-    <col min="4" max="4" width="11.42578125" style="4"/>
-    <col min="5" max="5" width="20.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="8"/>
-    <col min="7" max="7" width="16.85546875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="8"/>
-    <col min="9" max="9" width="20.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="12"/>
-    <col min="11" max="11" width="16.85546875" style="11" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" style="12"/>
-    <col min="13" max="13" width="20.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="12"/>
-    <col min="15" max="15" width="16.85546875" style="11" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="12"/>
-    <col min="17" max="17" width="11.42578125" style="22"/>
-    <col min="18" max="18" width="11.42578125" style="23"/>
+    <col min="3" max="3" width="11.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="26" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="27"/>
+    <col min="11" max="11" width="13.42578125" style="26" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" style="27"/>
+    <col min="13" max="13" width="14.140625" style="26" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="27"/>
+    <col min="15" max="15" width="12.7109375" style="26" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="27"/>
+    <col min="17" max="17" width="22" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="16" t="s">
+    <row r="2" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="13"/>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="13"/>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="14"/>
-      <c r="K2" s="17" t="s">
+      <c r="J2" s="23"/>
+      <c r="K2" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="14"/>
-      <c r="M2" s="17" t="s">
+      <c r="L2" s="23"/>
+      <c r="M2" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="N2" s="14"/>
-      <c r="O2" s="17" t="s">
+      <c r="N2" s="23"/>
+      <c r="O2" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="21"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="14"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="Q3" s="22">
-        <f>P3+N3+L3+J3+H3+F3</f>
+      <c r="E3" s="17">
+        <v>0</v>
+      </c>
+      <c r="F3" s="18">
+        <f>E3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="17">
+        <v>0</v>
+      </c>
+      <c r="H3" s="18">
+        <f>G3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="24">
+        <v>0</v>
+      </c>
+      <c r="J3" s="25">
+        <f>I3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="24">
+        <v>0</v>
+      </c>
+      <c r="L3" s="25">
+        <f>K3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="24">
+        <v>0</v>
+      </c>
+      <c r="N3" s="25">
+        <f>M3</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="24">
+        <v>0</v>
+      </c>
+      <c r="P3" s="25">
+        <f>O3</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="19">
+        <f>F3+H3+J3+L3+N3+P3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>34</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="8">
-        <v>0</v>
-      </c>
-      <c r="I4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="Q4" s="22">
+      <c r="E4" s="17">
+        <v>0</v>
+      </c>
+      <c r="F4" s="18">
+        <f t="shared" ref="F4:F20" si="0">E4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0</v>
+      </c>
+      <c r="H4" s="18">
+        <f t="shared" ref="H4:H20" si="1">G4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="24">
+        <v>0</v>
+      </c>
+      <c r="J4" s="25">
+        <f t="shared" ref="J4:J22" si="2">I4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="24">
+        <v>0</v>
+      </c>
+      <c r="L4" s="25">
+        <f t="shared" ref="L4:L22" si="3">K4</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="25">
+        <f t="shared" ref="N4:N22" si="4">M4</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="24">
+        <v>0</v>
+      </c>
+      <c r="P4" s="25">
+        <f t="shared" ref="P4:P22" si="5">O4</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="19">
+        <f t="shared" ref="Q4:Q22" si="6">F4+H4+J4+L4+N4+P4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
         <v>35</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="7">
-        <v>0</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="Q5" s="22">
+      <c r="E5" s="17">
+        <v>0</v>
+      </c>
+      <c r="F5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I5" s="24">
+        <v>0</v>
+      </c>
+      <c r="J5" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="24">
+        <v>0</v>
+      </c>
+      <c r="L5" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M5" s="24">
+        <v>0</v>
+      </c>
+      <c r="N5" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="24">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="19">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>103</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="7">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="Q6" s="22">
+      <c r="E6" s="17">
+        <v>0</v>
+      </c>
+      <c r="F6" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I6" s="24">
+        <v>0</v>
+      </c>
+      <c r="J6" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="24">
+        <v>0</v>
+      </c>
+      <c r="L6" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="24">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="19">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
         <v>208</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="Q7" s="22">
+      <c r="E7" s="17">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0</v>
+      </c>
+      <c r="J7" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="24">
+        <v>0</v>
+      </c>
+      <c r="L7" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0</v>
+      </c>
+      <c r="N7" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="24">
+        <v>0</v>
+      </c>
+      <c r="P7" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="19">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
         <v>221</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="Q8" s="22">
+      <c r="E8" s="17">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="17">
+        <v>1</v>
+      </c>
+      <c r="H8" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="24">
+        <v>0</v>
+      </c>
+      <c r="J8" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="24">
+        <v>0</v>
+      </c>
+      <c r="L8" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="24">
+        <v>0</v>
+      </c>
+      <c r="N8" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="24">
+        <v>0</v>
+      </c>
+      <c r="P8" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="19">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
         <v>319</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="7">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="Q9" s="22">
+      <c r="E9" s="17">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="24">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="24">
+        <v>0</v>
+      </c>
+      <c r="L9" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="24">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="24">
+        <v>0</v>
+      </c>
+      <c r="P9" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="19">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
         <v>329</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="7">
-        <v>0</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="Q10" s="22">
-        <v>0</v>
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="24">
+        <v>0</v>
+      </c>
+      <c r="J10" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="24">
+        <v>0</v>
+      </c>
+      <c r="L10" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="24">
+        <v>1</v>
+      </c>
+      <c r="N10" s="25">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="24">
+        <v>0</v>
+      </c>
+      <c r="P10" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="19">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
         <v>334</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="7">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="Q11" s="22">
+      <c r="E11" s="17">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="24">
+        <v>0</v>
+      </c>
+      <c r="J11" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="24">
+        <v>0</v>
+      </c>
+      <c r="L11" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="24">
+        <v>0</v>
+      </c>
+      <c r="N11" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O11" s="24">
+        <v>0</v>
+      </c>
+      <c r="P11" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="19">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
         <v>337</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0</v>
-      </c>
-      <c r="I12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="Q12" s="22">
+      <c r="E12" s="17">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="24">
+        <v>0</v>
+      </c>
+      <c r="J12" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="24">
+        <v>0</v>
+      </c>
+      <c r="L12" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="24">
+        <v>0</v>
+      </c>
+      <c r="N12" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="24">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="19">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
         <v>360</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7">
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
         <v>2</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="18">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="I13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="Q13" s="22">
+      <c r="I13" s="24">
+        <v>0</v>
+      </c>
+      <c r="J13" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K13" s="24">
+        <v>0</v>
+      </c>
+      <c r="L13" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="24">
+        <v>0</v>
+      </c>
+      <c r="N13" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="24">
+        <v>0</v>
+      </c>
+      <c r="P13" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="19">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
         <v>361</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="7">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-      <c r="I14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="Q14" s="22">
-        <v>0</v>
+      <c r="E14" s="17">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="24">
+        <v>0</v>
+      </c>
+      <c r="J14" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="24">
+        <v>0</v>
+      </c>
+      <c r="L14" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M14" s="24">
+        <v>1</v>
+      </c>
+      <c r="N14" s="25">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O14" s="24">
+        <v>0</v>
+      </c>
+      <c r="P14" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q14" s="19">
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
         <v>392</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="17">
         <v>3</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="18">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G15" s="7">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="Q15" s="22">
-        <v>3</v>
+      <c r="G15" s="17">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I15" s="24">
+        <v>2</v>
+      </c>
+      <c r="J15" s="25">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="K15" s="24">
+        <v>0</v>
+      </c>
+      <c r="L15" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="24">
+        <v>1</v>
+      </c>
+      <c r="N15" s="25">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O15" s="24">
+        <v>0</v>
+      </c>
+      <c r="P15" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q15" s="19">
+        <f t="shared" si="6"/>
+        <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
         <v>400</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>0</v>
-      </c>
-      <c r="I16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="Q16" s="22">
-        <v>1</v>
+      <c r="E16" s="17">
+        <v>1</v>
+      </c>
+      <c r="F16" s="18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="24">
+        <v>1</v>
+      </c>
+      <c r="J16" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="24">
+        <v>0</v>
+      </c>
+      <c r="L16" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="24">
+        <v>0</v>
+      </c>
+      <c r="N16" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="24">
+        <v>0</v>
+      </c>
+      <c r="P16" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="19">
+        <f t="shared" si="6"/>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="A17" s="15">
         <v>401</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="Q17" s="22">
+      <c r="E17" s="17">
+        <v>0</v>
+      </c>
+      <c r="F17" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="24">
+        <v>0</v>
+      </c>
+      <c r="J17" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="24">
+        <v>0</v>
+      </c>
+      <c r="L17" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="24">
+        <v>0</v>
+      </c>
+      <c r="N17" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="24">
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="19">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="A18" s="15">
         <v>407</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="8">
-        <v>0</v>
-      </c>
-      <c r="I18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="Q18" s="22">
+      <c r="E18" s="17">
+        <v>0</v>
+      </c>
+      <c r="F18" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="17">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="24">
+        <v>0</v>
+      </c>
+      <c r="J18" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="24">
+        <v>0</v>
+      </c>
+      <c r="L18" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="24">
+        <v>0</v>
+      </c>
+      <c r="N18" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="24">
+        <v>0</v>
+      </c>
+      <c r="P18" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="19">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19" s="15">
         <v>408</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="7">
-        <v>0</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0</v>
-      </c>
-      <c r="G19" s="7">
+      <c r="E19" s="17">
+        <v>0</v>
+      </c>
+      <c r="F19" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G19" s="17">
         <v>3</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="18">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="I19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="Q19" s="22">
+      <c r="I19" s="24">
+        <v>0</v>
+      </c>
+      <c r="J19" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="24">
+        <v>0</v>
+      </c>
+      <c r="L19" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="24">
+        <v>0</v>
+      </c>
+      <c r="N19" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="24">
+        <v>0</v>
+      </c>
+      <c r="P19" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="19">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20" s="15">
         <v>409</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <v>1</v>
-      </c>
-      <c r="H20" s="8">
-        <v>1</v>
-      </c>
-      <c r="I20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="Q20" s="22">
-        <v>2</v>
+      <c r="E20" s="17">
+        <v>1</v>
+      </c>
+      <c r="F20" s="18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G20" s="17">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I20" s="24">
+        <v>1</v>
+      </c>
+      <c r="J20" s="25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="K20" s="24">
+        <v>0</v>
+      </c>
+      <c r="L20" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="24">
+        <v>1</v>
+      </c>
+      <c r="N20" s="25">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="24">
+        <v>0</v>
+      </c>
+      <c r="P20" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="19">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>412</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="24">
+        <v>0</v>
+      </c>
+      <c r="J21" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="24">
+        <v>0</v>
+      </c>
+      <c r="L21" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="24">
+        <v>0</v>
+      </c>
+      <c r="N21" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="24">
+        <v>0</v>
+      </c>
+      <c r="P21" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="19">
+        <f>F21+H21+J21+L21+N21+P21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>414</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="24">
+        <v>0</v>
+      </c>
+      <c r="J22" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="24">
+        <v>0</v>
+      </c>
+      <c r="L22" s="25">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="24">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="24">
+        <v>0</v>
+      </c>
+      <c r="P22" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="19">
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>